--- a/帝国时代2决定版 文明联盟 骑兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 骑兵流最优研究顺序 By RemonBo.xlsx
@@ -20,9 +20,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑兵本体强化'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑兵本体强化'!$A$1:$E$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·骑兵本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与骑兵流无关·可跳过'!$A$1:$D$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与骑兵流无关·可跳过'!$1:$1</definedName>
@@ -1890,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1928,844 +1928,871 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>骆驼和象兵单位的训练速度 +25%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>文德尔之遗（骑士系造成践踏伤害）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>附加范围/冲击伤害，团战更占优</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>骑士系对步兵的攻击 +1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>明光铠（骑兵单位近战护甲+4）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>骆驼和象兵单位的训练速度 +25%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵系视野 +2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>视野提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>骑士系对步兵的攻击 +1</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>魏</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>明光铠（骑兵单位近战护甲+4）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>骆驼骑兵攻速+20%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>象兵近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>象轿（象兵近战护甲+1/远程护甲+1）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>蒙古</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>斥候骑兵系视野 +2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>象兵移速+10%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>獠牙剑（象兵攻击+3）</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>象兵额外受伤-25%且抗招降</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害，正面更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>派（战车/象兵攻速+20%）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>罗马</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>附加范围/冲击伤害，团战更占优</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>可驻扎，受攻击时更安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>骑士系视野 +2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>视野提升</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>附加范围/冲击伤害，团战更占优</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>维京</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>波斯</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>骑士系对远程士兵的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>骆驼生命+25%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害，正面更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>骆驼骑兵攻速+20%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>象兵近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>象轿（象兵近战护甲+1/远程护甲+1）</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>医疗部队（象兵每分钟恢复30生命）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>象兵移速+10%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>獠牙剑（象兵攻击+3）</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>派（战车/象兵攻速+20%）</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>法兰克</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>骑士系视野 +2</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>马其顿人</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>维京</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>波斯</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>骑士系对远程士兵的攻击力 +2</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>马扎尔</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>骆驼生命+25%</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>契丹</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>直接强化骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>宝伞（象兵生命+100）</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>医疗部队（象兵每分钟恢复30生命）</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E32"/>
+  <autoFilter ref="A1:E33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2777,7 +2804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2815,19 +2842,19 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降</t>
+          <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2837,24 +2864,24 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>直接强化骑兵</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2868,35 +2895,8 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>拜占庭</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/帝国时代2决定版 文明联盟 骑兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 骑兵流最优研究顺序 By RemonBo.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑兵本体强化'!$A$1:$E$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑兵本体强化'!$A$1:$E$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·骑兵本体强化'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
@@ -596,31 +596,31 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>鞑靼（备选）</t>
+          <t>瓦兰吉人（备选）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>备选：原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>魏（备选）</t>
+          <t>鞑靼（备选）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
+          <t>备选：原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -638,17 +638,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>瞿折罗（首选）</t>
+          <t>契丹（首选）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%；斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
     </row>
@@ -656,13 +656,13 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>库曼（备选）</t>
+          <t>魏（备选）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
+          <t>备选：原生条目 3 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -670,13 +670,13 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>蒙古（备选）</t>
+          <t>库曼（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
+          <t>备选：原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
         </is>
       </c>
     </row>
@@ -694,17 +694,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>瓦兰吉人（首选）</t>
+          <t>瞿折罗（首选）</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
+          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -712,13 +712,13 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚（备选）</t>
+          <t>蒙古（备选）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
+          <t>备选：原生条目 2 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
         </is>
       </c>
     </row>
@@ -726,13 +726,13 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔（备选）</t>
+          <t>格鲁吉亚（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
+          <t>备选：原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -797,13 +797,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>明光铠（骑兵单位近战护甲+4）</t>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -853,17 +853,17 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51" customHeight="1">
+          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>明光铠（骑兵单位近战护甲+4）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系视野 +2</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
+          <t>原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
+          <t>斥候骑兵系视野 +2</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -963,27 +963,27 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>骆驼骑兵攻速+20%；斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
+          <t>马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、骑士、草原枪兵；最直接一条：骆驼骑兵攻速+20%</t>
+          <t>原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
+          <t>骆驼骑兵攻速+20%；斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、骑士、草原枪兵；最直接一条：骆驼骑兵攻速+20%</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>象兵移速+10%；獠牙剑（象兵攻击+3）</t>
+          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵移速+10%</t>
+          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
+          <t>象兵移速+10%；獠牙剑（象兵攻击+3）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：象兵额外受伤-25%且抗招降</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵移速+10%</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
+          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
+          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：象兵额外受伤-25%且抗招降</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
+          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,17 +1203,17 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>马厩科技研究+50%；萨加里斯斧（骑兵无法格挡伤害+2）</t>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,27 +1233,27 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>马厩科技-50%；城堡时代可升重装骑士</t>
+          <t>马厩科技研究+50%；萨加里斯斧（骑兵无法格挡伤害+2）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+          <t>马厩科技-50%；城堡时代可升重装骑士</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
+          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="51" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>骑士系视野 +2</t>
+          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,17 +1353,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
+          <t>骑士系视野 +2</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>古典时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+          <t>原生条目 4 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,17 +1383,17 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>古典时代起</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：象兵城堡/帝王费用-25/35%</t>
+          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
+          <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>帝王时代起</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>帝王时代起</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>骑士系对远程士兵的攻击力 +2</t>
+          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：骑士系对远程士兵的攻击力 +2</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>骑士系对远程士兵的攻击力 +2</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="51" customHeight="1">
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：骑士系对远程士兵的攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,17 +1573,17 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="51" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>骆驼生命+25%</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
+          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>骆驼生命+25%</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1935,49 +1935,49 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>契丹</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>骆驼和象兵单位的训练速度 +25%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>战斗中持续回血：攻速越快回得越多，是唯一的骑兵续航引擎，缠斗越久优势越大</t>
         </is>
       </c>
     </row>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>骑士系对步兵的攻击 +1</t>
+          <t>骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2043,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>明光铠（骑兵单位近战护甲+4）</t>
+          <t>文德尔之遗（骑士系造成践踏伤害）</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -2070,76 +2070,76 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>骑士系对步兵的攻击 +1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>明光铠（骑兵单位近战护甲+4）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>蒙古</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>斥候骑兵系视野 +2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>视野提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -2151,26 +2151,26 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>骆驼骑兵攻速+20%</t>
+          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1</t>
+          <t>骆驼骑兵攻速+20%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
@@ -2232,22 +2232,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>象轿（象兵近战护甲+1/远程护甲+1）</t>
+          <t>斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>象兵移速+10%</t>
+          <t>象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>獠牙剑（象兵攻击+3）</t>
+          <t>象轿（象兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2313,12 +2313,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降</t>
+          <t>象兵移速+10%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>减少受到的伤害，正面更耐打</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -2340,103 +2340,103 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>獠牙剑（象兵攻击+3）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>孟加拉</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>象兵额外受伤-25%且抗招降</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害，正面更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>派（战车/象兵攻速+20%）</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>罗马</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>立陶宛</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>可驻扎，受攻击时更安全</t>
         </is>
       </c>
     </row>
@@ -2448,22 +2448,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>骑士系视野 +2</t>
+          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -2475,22 +2475,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>可驻扎，受攻击时更安全</t>
         </is>
       </c>
     </row>
@@ -2502,22 +2502,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>骑士系视野 +2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -2529,22 +2529,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>骑士系对远程士兵的攻击力 +2</t>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2583,49 +2583,49 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>骆驼生命+25%</t>
+          <t>骑士系对远程士兵的攻击力 +2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
@@ -2637,22 +2637,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+          <t>骆驼生命+25%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>减少受到的伤害，正面更耐打</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2664,22 +2664,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
+          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>减少受到的伤害，正面更耐打</t>
         </is>
       </c>
     </row>
@@ -2691,22 +2691,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
+          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>宝伞（象兵生命+100）</t>
+          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2745,54 +2745,81 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>达罗毗荼</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>医疗部队（象兵每分钟恢复30生命）</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>色雷斯人</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E33"/>
+  <autoFilter ref="A1:E34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3526,22 +3553,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>13/20</t>
+          <t>14/20</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%；斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；骑兵科技树 13/20。缺：圣骑士、重装骑士、骑士、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 2 条（强 2）；骑兵科技树 14/20。缺：圣骑士、重装骑士、骑士、帝王骆驼兵、血统</t>
         </is>
       </c>
     </row>
@@ -3551,72 +3578,72 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>13/20</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+          <t>原生条目 3 条（强 2）；骑兵科技树 13/20。缺：圣骑士、重装骑士、骑士、帝王骆驼兵、草原枪兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18/20</t>
+          <t>14/20</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；骑兵科技树 18/20。缺：圣骑士、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 2）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>18/20</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>明光铠（骑兵单位近战护甲+4）</t>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1）；骑兵科技树 11/20。缺：圣骑士、重装骑士、骑士、骆驼兵、重装骆驼兵</t>
+          <t>原生条目 1 条（强 0）；骑兵科技树 18/20。缺：圣骑士、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -3626,22 +3653,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17/20</t>
+          <t>11/20</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75</t>
+          <t>明光铠（骑兵单位近战护甲+4）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0）；骑兵科技树 17/20。缺：重装骆驼兵、帝王骆驼兵、驯马</t>
+          <t>原生条目 3 条（强 1）；骑兵科技树 11/20。缺：圣骑士、重装骑士、骑士、骆驼兵、重装骆驼兵</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3678,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3661,12 +3688,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系视野 +2</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；骑兵科技树 17/20。缺：圣骑士、帝王骆驼兵、骑兵板甲</t>
+          <t>原生条目 3 条（强 0）；骑兵科技树 17/20。缺：重装骆驼兵、帝王骆驼兵、驯马</t>
         </is>
       </c>
     </row>
@@ -3676,22 +3703,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>17/20</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
+          <t>斥候骑兵系视野 +2</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 2 条（强 1）；骑兵科技树 17/20。缺：圣骑士、帝王骆驼兵、骑兵板甲</t>
         </is>
       </c>
     </row>
@@ -3701,22 +3728,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16/20</t>
+          <t>14/20</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1）；骑兵科技树 16/20。缺：圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵</t>
+          <t>原生条目 2 条（强 0）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -3726,22 +3753,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15/20</t>
+          <t>16/20</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>骆驼骑兵攻速+20%；斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
+          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；骑兵科技树 15/20。缺：圣骑士、重装骑士、骑士、草原枪兵、精锐草原枪兵</t>
+          <t>原生条目 3 条（强 1）；骑兵科技树 16/20。缺：圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵</t>
         </is>
       </c>
     </row>
@@ -3751,22 +3778,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>15/20</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
+          <t>骆驼骑兵攻速+20%；斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 2 条（强 2）；骑兵科技树 15/20。缺：圣骑士、重装骑士、骑士、草原枪兵、精锐草原枪兵</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3803,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3786,12 +3813,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>象兵移速+10%；獠牙剑（象兵攻击+3）</t>
+          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 3 条（强 2）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -3801,22 +3828,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>14/20</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
+          <t>象兵移速+10%；獠牙剑（象兵攻击+3）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；骑兵科技树 11/20。缺：圣骑士、重装骑士、骑士、骠骑兵、骆驼兵</t>
+          <t>原生条目 2 条（强 2）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -3826,22 +3853,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16/20</t>
+          <t>11/20</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
+          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；骑兵科技树 16/20。缺：圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵</t>
+          <t>原生条目 3 条（强 2）；骑兵科技树 11/20。缺：圣骑士、重装骑士、骑士、骠骑兵、骆驼兵</t>
         </is>
       </c>
     </row>
@@ -3851,22 +3878,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>15/20</t>
+          <t>16/20</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0）；骑兵科技树 15/20。缺：骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵、精锐草原枪兵</t>
+          <t>原生条目 2 条（强 1）；骑兵科技树 16/20。缺：圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3989,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>契丹</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -3977,12 +4004,12 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>掷矛/长矛/斥候骑兵系训练升级+15%；斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4019,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -4007,22 +4034,22 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -4037,22 +4064,22 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4067,22 +4094,22 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>明光铠（骑兵单位近战护甲+4）</t>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
+          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -4097,22 +4124,22 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>明光铠（骑兵单位近战护甲+4）</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>蒙古</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4127,12 +4154,12 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>斥候骑兵系视野 +2</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
+          <t>原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4169,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>蒙古</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4157,22 +4184,22 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
+          <t>斥候骑兵系视野 +2</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -4187,22 +4214,22 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>印度斯坦</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4217,12 +4244,12 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>骆驼骑兵攻速+20%；斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
+          <t>马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、骑士、草原枪兵；最直接一条：骆驼骑兵攻速+20%</t>
+          <t>原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4259,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>缅甸</t>
+          <t>印度斯坦</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4247,12 +4274,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
+          <t>骆驼骑兵攻速+20%；斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、骑士、草原枪兵；最直接一条：骆驼骑兵攻速+20%</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4289,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>高棉</t>
+          <t>缅甸</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4277,12 +4304,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>象兵移速+10%；獠牙剑（象兵攻击+3）</t>
+          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵移速+10%</t>
+          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4319,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>孟加拉</t>
+          <t>高棉</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4307,12 +4334,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
+          <t>象兵移速+10%；獠牙剑（象兵攻击+3）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：象兵额外受伤-25%且抗招降</t>
+          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵移速+10%</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4349,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>孟加拉</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4337,12 +4364,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
+          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
+          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：象兵额外受伤-25%且抗招降</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4379,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4367,12 +4394,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4409,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -4397,12 +4424,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
+          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4439,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -4427,12 +4454,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>马厩科技研究+50%；萨加里斯斧（骑兵无法格挡伤害+2）</t>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4469,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -4457,22 +4484,22 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>马厩科技-50%；城堡时代可升重装骑士</t>
+          <t>马厩科技研究+50%；萨加里斯斧（骑兵无法格挡伤害+2）</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="51" customHeight="1">
+          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>罗马</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -4487,12 +4514,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+          <t>马厩科技-50%；城堡时代可升重装骑士</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4529,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>罗马</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -4517,22 +4544,22 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
+          <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -4547,12 +4574,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>骑士系视野 +2</t>
+          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4589,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -4577,12 +4604,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
+          <t>骑士系视野 +2</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+          <t>原生条目 4 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4619,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -4607,12 +4634,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4649,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -4637,12 +4664,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：象兵城堡/帝王费用-25/35%</t>
+          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4679,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -4667,12 +4694,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
+          <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4709,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -4697,12 +4724,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4739,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -4727,12 +4754,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>骑士系对远程士兵的攻击力 +2</t>
+          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：骑士系对远程士兵的攻击力 +2</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4769,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -4757,22 +4784,22 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>骑士系对远程士兵的攻击力 +2</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="51" customHeight="1">
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：骑士系对远程士兵的攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -4787,22 +4814,22 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
+          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="51" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -4817,12 +4844,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>骆驼生命+25%</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
+          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4859,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>契丹</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -4847,12 +4874,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>骆驼生命+25%</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5882,107 +5909,111 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr"/>
+    <row r="9" ht="49" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>决定性前提 4</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>契丹「斡鲁朵骑兵」是全表唯一的骑兵「战斗中回血」——实现方式是把 dat 的骑兵类与斥候类统一加上战斗回血，覆盖面极广（骆驼/象兵/战象这类非马厩骑兵也吃）。它与攻速乘算：攻速越快，单位时间回血越多，所以「保加利亚马镫 + 契丹斡鲁朵」是全套按钮里唯一的吸血组合，故两者并列本表前二。</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>模组专属：按钮机制</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>开局 3 个免费按钮位；之后每个按钮 2000 金。一个按钮只能研究一次，重复研究等于白花。</t>
-        </is>
-      </c>
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="B10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>模组专属：无专属机制</t>
+          <t>模组专属：按钮机制</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>已确认模组文本中没有针对骑兵的独立按钮或 SSR 互斥项。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1">
+          <t>开局 3 个免费按钮位；之后每个按钮 2000 金。一个按钮只能研究一次，重复研究等于白花。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="49" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
+          <t>模组专属：契丹斡鲁朵骑兵按「骑兵类」判定，象兵也算骑兵</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>斡鲁朵骑兵的实现（游戏自带 Effects.xs 的函数 #3）是给 dat class 12（骑兵）与 class 47（斥候）加 CombatAbility 128，再逐个剔除少数单位。全部象兵系单位里，战斗象/装甲象/战象的类别都是 12（骑兵），所以它们同样吃这个战斗回血；只有骑象弓兵（class 36）不吃，重弩战象（Ballista Elephant）被显式剔除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>模组专属：无骑兵 SSR</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>除上述外，模组文本中没有针对骑兵的独立按钮或 SSR 互斥项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
           <t>排序口径</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>① 只看直接作用于骑兵本体、或其前置/费用/产出的条目；</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与骑兵流无关·可跳过」）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="12" t="inlineStr"/>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="12" t="inlineStr"/>
-      <c r="B15" s="12" t="inlineStr"/>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>② 泛用条目与兵种类一律剔除（放进「与骑兵流无关·可跳过」）；</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr"/>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="12" t="inlineStr"/>
+      <c r="B17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>未验证项</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="12" t="inlineStr"/>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>★ 最重要的一条：别买重复</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
@@ -5990,29 +6021,49 @@
       <c r="A20" s="12" t="inlineStr"/>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="12" t="inlineStr"/>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
           <t>整理</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>By RemonBo；本表由 DSH 生成。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 骑兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 骑兵流最优研究顺序 By RemonBo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开局3免费位" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续2000金顺序" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甲类·骑兵本体强化" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·费用与前置" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乙类·减费用与资源效率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="与骑兵流无关·可跳过" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主选文明推荐" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全62文明总名次" sheetId="7" state="visible" r:id="rId7"/>
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑兵本体强化'!$A$1:$E$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑兵本体强化'!$A$1:$E$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·骑兵本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·费用与前置'!$A$1:$E$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·费用与前置'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与骑兵流无关·可跳过'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与骑兵流无关·可跳过'!$A$1:$D$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与骑兵流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -592,11 +592,11 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：马镫（骑兵攻速+33%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：马镫（骑兵攻速+33%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -606,11 +606,11 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>第 3 位</t>
@@ -699,12 +699,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%；骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
+          <t>备选：阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -797,7 +797,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>4</v>
       </c>
@@ -823,11 +823,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>5</v>
       </c>
@@ -853,11 +853,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>6</v>
       </c>
@@ -873,7 +873,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>明光铠（骑兵单位近战护甲+4）</t>
+          <t>明光铠（骑兵单位近战护甲+4）；黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%；骑兵对攻城武器的攻击力 +2</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系视野 +2</t>
+          <t>斥候骑兵系视野 +2；斥候/草原枪兵城堡/帝王生命+20/30%</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
         </is>
       </c>
     </row>
@@ -1033,11 +1033,11 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、骑士、草原枪兵；最直接一条：骆驼骑兵攻速+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、骑士、草原枪兵；最直接一条：骆驼骑兵攻速+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>12</v>
       </c>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
+          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）；曼尼普尔马（骑兵对远程攻+4）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵移速+10%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵移速+10%</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
+          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）；骑兵对掷矛手攻+2</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1123,11 +1123,11 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：象兵额外受伤-25%且抗招降</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：象兵额外受伤-25%且抗招降</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>15</v>
       </c>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
+          <t>西帕希骑兵（骑射手生命+20）</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
+          <t>掠夺者（马厩训练答刺罕骑兵）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>骑士系视野 +2</t>
+          <t>骑士系视野 +2；骑兵封建起生命+20%；王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
         </is>
       </c>
     </row>
@@ -1393,11 +1393,11 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>24</v>
       </c>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）；兵营/靶场/马厩可用招募训令；步兵护甲升级适用于骑兵</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,27 +1443,27 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>帝王时代起</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：象兵城堡/帝王费用-25/35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="51" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
+          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>帝王时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>骑士系对远程士兵的攻击力 +2</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：骑士系对远程士兵的攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="51" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>骑士系对远程士兵的攻击力 +2</t>
+          <t>后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：骑士系对远程士兵的攻击力 +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="51" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,17 +1573,17 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>骆驼生命+25%</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="51" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>骆驼生命+25%</t>
+          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+          <t>斥候骑兵系对远程士兵的攻击力 +1；列克提克遗产（斥候系可造成践踏伤害）</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：斥候骑兵系对远程士兵的攻击力 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="51" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
+          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 1 / 弱 3）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：斥候骑兵系对远程士兵的攻击力 +1</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
+          <t>宝伞（象兵生命+100）</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="51" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>宝伞（象兵生命+100）</t>
+          <t>医疗部队（象兵每分钟恢复30生命）；乌兹钢（步兵和骑兵攻击无视护甲）</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1753,17 +1753,17 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：宝伞（象兵生命+100）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：医疗部队（象兵每分钟恢复30生命）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="51" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>医疗部队（象兵每分钟恢复30生命）</t>
+          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）；奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：医疗部队（象兵每分钟恢复30生命）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+          <t>死士（骑兵攻击+5）</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骠骑兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -1833,27 +1833,27 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>死士（骑兵攻击+5）</t>
+          <t>骑兵杀敌+3黄金；Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骠骑兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>骑兵杀敌+3黄金；Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1873,12 +1873,42 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 3）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：象兵城堡/帝王费用-25/35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F37"/>
+  <autoFilter ref="A1:F38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1890,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1935,76 +1965,76 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>马镫（骑兵攻速+33%）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>契丹</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>掷矛/长矛/斥候骑兵系训练升级+15%</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>契丹</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>斡鲁朵骑兵（骑兵战斗中回血）</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>战斗中持续回血：攻速越快回得越多，是唯一的骑兵续航引擎，缠斗越久优势越大</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>瞿折罗</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2021,66 +2051,66 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
           <t>骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>瓦兰吉人</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
-        </is>
-      </c>
-    </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>骑士系对步兵的攻击 +1</t>
+          <t>骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -2097,12 +2127,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>明光铠（骑兵单位近战护甲+4）</t>
+          <t>文德尔之遗（骑士系造成践踏伤害）</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2112,7 +2142,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -2124,265 +2154,265 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>瓦兰吉人</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>骑士系对步兵的攻击 +1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>鞑靼</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>明光铠（骑兵单位近战护甲+4）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>骑兵对攻城武器的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>靶场/马厩木材-75</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>蒙古</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>斥候骑兵系视野 +2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>视野提升</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>斥候/草原枪兵城堡/帝王生命+20/30%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>骆驼骑兵攻速+20%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>攻速提升，直接抬高输出</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>印度斯坦</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>象兵近战护甲+1/远程护甲+1</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>缅甸</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>象轿（象兵近战护甲+1/远程护甲+1）</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>象兵移速+10%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>机动性提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>高棉</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>獠牙剑（象兵攻击+3）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>孟加拉</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>象兵额外受伤-25%且抗招降</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>减少受到的伤害，正面更耐打</t>
         </is>
       </c>
     </row>
@@ -2394,432 +2424,1269 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>持续回血，长期更省维修成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>骆驼骑兵攻速+20%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>攻速提升，直接抬高输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>印度斯坦</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵和骆驼单位对建筑的攻击力 +2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>象兵近战护甲+1/远程护甲+1</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>象轿（象兵近战护甲+1/远程护甲+1）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>曼尼普尔马（骑兵对远程攻+4）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>象兵移速+10%</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>机动性提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>高棉</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>獠牙剑（象兵攻击+3）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>孟加拉</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>象兵额外受伤-25%且抗招降</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害，正面更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>派（战车/象兵攻速+20%）</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>孟加拉</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>骑兵对掷矛手攻+2</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>土耳其</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>西帕希骑兵（骑射手生命+20）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>掠夺者（马厩训练答刺罕骑兵）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>直接强化骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>条顿</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>马厩科技研究+50%</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>直接强化骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>阿契美尼德</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>萨加里斯斧（骑兵无法格挡伤害+2）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>马厩科技-50%</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>勃艮第</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>城堡时代可升重装骑士</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>直接强化骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>罗马</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>立陶宛</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>可驻扎，受攻击时更安全</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>法兰克</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>骑士系视野 +2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>视野提升</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>骑兵封建起生命+20%</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>普鲁人</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>持续回血，长期更省维修成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>马其顿人</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>兵营/靶场/马厩可用招募训令</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>提前解锁，抢一个时代的节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>马其顿人</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>步兵护甲升级适用于骑兵</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>吴</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>维京</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>波斯</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>骑士系对远程士兵的攻击力 +2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>团队加成</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>附加范围/冲击伤害，团战更占优</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>马扎尔</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>萨拉森</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>骆驼生命+25%</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>萨拉森</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>骆驼生命+25%</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>减少受到的伤害，正面更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>列克提克遗产（斥候系可造成践踏伤害）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>附加范围/冲击伤害，团战更占优</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>西西里</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>医疗部队（象兵每分钟恢复30生命）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>生命值提升，抗打更久</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>达罗毗荼</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>乌兹钢（步兵和骑兵攻击无视护甲）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>攻击无视护甲，克制重甲目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>色雷斯人</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>额外产出资源，经济滚雪球更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>死士（骑兵攻击+5）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>攻击力提升，正面更硬</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>骑兵杀敌+3黄金</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>资源产出/节省，加快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>减少受到的伤害，正面更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>团队加成</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>西西里</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>越南</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>宝伞（象兵生命+100）</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>达罗毗荼</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>医疗部队（象兵每分钟恢复30生命）</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>护甲提升，减伤更耐打</t>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>穿透伤害，对高护甲目标有效</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E34"/>
+  <autoFilter ref="A1:E65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2831,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2869,61 +3736,331 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>格鲁吉亚</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>柏柏尔</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>马厩单位城堡/帝王费用-15/20%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>匈奴</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>马厩工作速度 +20%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>骑士精神（马厩工作速度+40%）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>工作速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>斥候系费用-15%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>血统/斥候食物费用-50%</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>贵族特权（骑士黄金费用-60%）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>马来</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>拜占庭</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>所有单位黄金费用-20%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -2935,7 +4072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3189,12 +4326,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>海军和火药文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -3204,19 +4341,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -3226,19 +4363,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3248,19 +4385,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3270,19 +4407,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>弓兵与步兵文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3292,19 +4429,19 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>火药和僧侣文明</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3314,19 +4451,19 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>火药和僧侣文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3336,19 +4473,19 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>步兵和海军文明</t>
+          <t>弓兵和海军文明</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3358,19 +4495,19 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>弓兵和海军文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3380,19 +4517,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3402,19 +4539,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -3424,19 +4561,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -3446,34 +4583,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强骑兵</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D24"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3953,7 +5068,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -3979,11 +5094,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：马镫（骑兵攻速+33%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：马镫（骑兵攻速+33%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -4009,11 +5124,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：掷矛/长矛/斥候骑兵系训练升级+15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -4034,16 +5149,16 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%；骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -4069,11 +5184,11 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -4099,11 +5214,11 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -4124,12 +5239,12 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>明光铠（骑兵单位近战护甲+4）</t>
+          <t>明光铠（骑兵单位近战护甲+4）；黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%；骑兵对攻城武器的攻击力 +2</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 2）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骆驼兵；最直接一条：明光铠（骑兵单位近战护甲+4）</t>
         </is>
       </c>
     </row>
@@ -4159,7 +5274,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
         </is>
       </c>
     </row>
@@ -4184,12 +5299,12 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>斥候骑兵系视野 +2</t>
+          <t>斥候骑兵系视野 +2；斥候/草原枪兵城堡/帝王生命+20/30%</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 17/20；缺 圣骑士、帝王骆驼兵、骑兵板甲；最直接一条：斥候骑兵系视野 +2</t>
         </is>
       </c>
     </row>
@@ -4214,12 +5329,12 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -4249,7 +5364,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
         </is>
       </c>
     </row>
@@ -4279,11 +5394,11 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、骑士、草原枪兵；最直接一条：骆驼骑兵攻速+20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、骑士、草原枪兵；最直接一条：骆驼骑兵攻速+20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -4304,12 +5419,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
+          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）；曼尼普尔马（骑兵对远程攻+4）</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵近战护甲+1/远程护甲+1</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵近战护甲+1/远程护甲+1</t>
         </is>
       </c>
     </row>
@@ -4339,7 +5454,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵移速+10%</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：象兵移速+10%</t>
         </is>
       </c>
     </row>
@@ -4364,16 +5479,16 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
+          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）；骑兵对掷矛手攻+2</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2 / 弱 1）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：象兵额外受伤-25%且抗招降</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑兵科技树 11/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：象兵额外受伤-25%且抗招降</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="51" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -4394,12 +5509,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
+          <t>西帕希骑兵（骑射手生命+20）</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
     </row>
@@ -4424,12 +5539,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
+          <t>掠夺者（马厩训练答刺罕骑兵）</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -4459,7 +5574,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
         </is>
       </c>
     </row>
@@ -4489,7 +5604,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -4519,7 +5634,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -4549,7 +5664,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：野战军（民兵系/骑士系/百夫长训练+50%，获冲锋攻击）</t>
         </is>
       </c>
     </row>
@@ -4579,7 +5694,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
     </row>
@@ -4604,12 +5719,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>骑士系视野 +2</t>
+          <t>骑士系视野 +2；骑兵封建起生命+20%；王家敕令骑兵（骑马弩手黄金-40%）</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
         </is>
       </c>
     </row>
@@ -4639,11 +5754,11 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -4664,12 +5779,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）；兵营/靶场/马厩可用招募训令；步兵护甲升级适用于骑兵</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
     </row>
@@ -4679,7 +5794,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -4694,22 +5809,22 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：象兵城堡/帝王费用-25/35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="51" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -4724,22 +5839,22 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
+          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="51" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>波斯</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -4754,22 +5869,22 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>骑士系对远程士兵的攻击力 +2</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：骑士系对远程士兵的攻击力 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="51" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>波斯</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -4784,22 +5899,22 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>骑士系对远程士兵的攻击力 +2</t>
+          <t>后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：骑士系对远程士兵的攻击力 +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="51" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -4814,22 +5929,22 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -4844,22 +5959,22 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>骆驼生命+25%</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="51" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -4874,12 +5989,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>骆驼生命+25%</t>
+          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
         </is>
       </c>
     </row>
@@ -4889,7 +6004,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -4904,22 +6019,22 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+          <t>斥候骑兵系对远程士兵的攻击力 +1；列克提克遗产（斥候系可造成践踏伤害）</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：斥候骑兵系对远程士兵的攻击力 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="51" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -4934,12 +6049,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
+          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>原生条目 4 条（强 1 / 弱 3）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：斥候骑兵系对远程士兵的攻击力 +1</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
     </row>
@@ -4949,7 +6064,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -4964,22 +6079,22 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
+          <t>宝伞（象兵生命+100）</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="51" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -4994,22 +6109,22 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>宝伞（象兵生命+100）</t>
+          <t>医疗部队（象兵每分钟恢复30生命）；乌兹钢（步兵和骑兵攻击无视护甲）</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 1 / 弱 0）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：宝伞（象兵生命+100）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：医疗部队（象兵每分钟恢复30生命）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="51" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -5024,22 +6139,22 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>医疗部队（象兵每分钟恢复30生命）</t>
+          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）；奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：医疗部队（象兵每分钟恢复30生命）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -5054,12 +6169,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+          <t>死士（骑兵攻击+5）</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骠骑兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -5069,7 +6184,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -5084,22 +6199,22 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>死士（骑兵攻击+5）</t>
+          <t>骑兵杀敌+3黄金；Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骠骑兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>马来</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -5114,12 +6229,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>骑兵杀敌+3黄金；Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）；布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0 / 弱 3）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：象兵城堡/帝王费用-25/35%</t>
         </is>
       </c>
     </row>
@@ -5129,7 +6244,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -5139,17 +6254,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强骑兵</t>
+          <t>所有单位黄金费用-20%</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵</t>
         </is>
       </c>
     </row>
@@ -5159,7 +6274,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -5179,7 +6294,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -5189,7 +6304,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -5209,7 +6324,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -5219,7 +6334,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -5239,7 +6354,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -5249,7 +6364,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -5269,7 +6384,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -5279,7 +6394,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -5299,7 +6414,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -5309,7 +6424,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -5329,7 +6444,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -5339,7 +6454,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -5359,7 +6474,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -5369,7 +6484,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -5389,7 +6504,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -5399,7 +6514,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -5419,7 +6534,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -5429,7 +6544,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -5449,7 +6564,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>海军和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「采果工产食+木材」）</t>
+          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
         </is>
       </c>
     </row>
@@ -5826,7 +6941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5969,101 +7084,141 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>① 只看直接作用于骑兵本体、或其前置/费用/产出的条目；</t>
+          <t>本表按用户打法口径分四个阶段排序：先加强要玩的主流派兵种，再减它的资源消耗，最后才补资源效率。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>① 阶段 1 · 本体强化</t>
+        </is>
+      </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>② 泛用条目与兵种类一律剔除（放进「与骑兵流无关·可跳过」）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="12" t="inlineStr"/>
+          <t>直接加强骑兵本体的条目（攻击/护甲/生命/攻速/射程/移速/回血/数量/生产训练速度/解锁升级等）。这一档最优先。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>② 阶段 2 · 减费用</t>
+        </is>
+      </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>③ 门槛越低、替代成本越高，名次越靠前。</t>
+          <t>降低该兵种及同系兵种（马厩骑兵系（象兵也属骑兵类））生产所需资源的条目：费用/成本 -N%、升级免费、用其它资源替代。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="12" t="inlineStr"/>
-      <c r="B17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>③ 阶段 3 · 资源效率</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>采集/产出/携带/贸易/人口/经济科技等让主流派更快成型的条目。</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>未验证项</t>
+          <t>④ 阶段 4 · 其他相关</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
+          <t>其余与本流派相关、但不属于上述三类的条目。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>★ 最重要的一条：别买重复</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
+          <t>同阶段内按「人工权威顺序（实战强度）」再排；泛用条目与兵种类一律剔除（放进「与骑兵流无关·可跳过」）。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="12" t="inlineStr"/>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
-        </is>
-      </c>
+      <c r="B20" s="12" t="inlineStr"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>数据来源</t>
+          <t>未验证项</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+          <t>本表的档位与名次为依据「条目文本 + 官方科技树」的经验判断，未逐项实测；与实战不符时以实战为准。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>★ 最重要的一条：别买重复</t>
+        </is>
+      </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+          <t>主选文明已经自带的加成，不要再用按钮买一遍——一个按钮只能研究一次，重复等于白花 2000 金。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>整理</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>By RemonBo；本表由 DSH 生成。</t>
+          <t>正确流程是：先定主选文明（见「主选文明推荐」），再按剩下的缺口挑 3 个免费位。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>用户提供的 62 张文明卡片 PNG（By RemonBo）+ 游戏官方简体中文字串逐条核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="12" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>主选文明的科技树数据来自游戏官方 CivTechTrees 的 62 份 JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>整理</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>By RemonBo；本表由 DSH 生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
           <t>与本表配套</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>同目录下的箭塔流、炮塔流与其余流派总表。</t>
         </is>

--- a/帝国时代2决定版 文明联盟 骑兵流最优研究顺序 By RemonBo.xlsx
+++ b/帝国时代2决定版 文明联盟 骑兵流最优研究顺序 By RemonBo.xlsx
@@ -18,13 +18,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'开局3免费位'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后续2000金顺序'!$A$1:$F$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'后续2000金顺序'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑兵本体强化'!$A$1:$E$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'甲类·骑兵本体强化'!$A$1:$E$62</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'甲类·骑兵本体强化'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'乙类·减费用与资源效率'!$A$1:$E$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'乙类·减费用与资源效率'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与骑兵流无关·可跳过'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'与骑兵流无关·可跳过'!$A$1:$D$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'与骑兵流无关·可跳过'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'主选文明推荐'!$A$1:$E$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'主选文明推荐'!$1:$1</definedName>
@@ -600,27 +600,27 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人（备选）</t>
+          <t>瞿折罗（备选）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>备选：阶段1·本体强化；原生条目 6 条（强 2 / 弱 2）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>鞑靼（备选）</t>
+          <t>瓦兰吉人（备选）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
+          <t>备选：阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
         </is>
       </c>
     </row>
@@ -670,13 +670,13 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>库曼（备选）</t>
+          <t>鞑靼（备选）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
+          <t>备选：阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="51" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>第 3 位</t>
@@ -694,17 +694,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>瞿折罗（首选）</t>
+          <t>法兰克（首选）</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%；骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
+          <t>骑士系视野 +2；骑兵封建起生命+20%；骑士精神（马厩工作速度+40%）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
         </is>
       </c>
     </row>
@@ -726,13 +726,13 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚（备选）</t>
+          <t>库曼（备选）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>备选：阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
+          <t>备选：阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%；骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 2）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
         </is>
       </c>
     </row>
@@ -887,13 +887,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="51" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>封建时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）；曼尼普尔马（骑兵对远程攻+4）</t>
+          <t>曼尼普尔马（骑兵对远程攻+4）；象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）；骑兵对掷矛手攻+2</t>
+          <t>骑兵对掷矛手攻+2；象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="51" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>西帕希骑兵（骑射手生命+20）</t>
+          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>掠夺者（马厩训练答刺罕骑兵）</t>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1203,17 +1203,17 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+          <t>萨加里斯斧（骑兵无法格挡伤害+2）；马厩科技研究+50%</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1233,27 +1233,27 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>马厩科技研究+50%；萨加里斯斧（骑兵无法格挡伤害+2）</t>
+          <t>城堡时代可升重装骑士</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="51" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>马厩科技-50%；城堡时代可升重装骑士</t>
+          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
     </row>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="51" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1323,27 +1323,27 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
+          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>古典时代起</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>骑士系视野 +2；骑兵封建起生命+20%；王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>斥候骑兵系对远程士兵的攻击力 +1；列克提克遗产（斥候系可造成践踏伤害）</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1363,17 +1363,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：斥候骑兵系对远程士兵的攻击力 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="51" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1383,27 +1383,27 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）；步兵护甲升级适用于骑兵；兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>古典时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）；兵营/靶场/马厩可用招募训令；步兵护甲升级适用于骑兵</t>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>帝王时代起</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
+          <t>骑兵杀敌+3黄金；Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>帝王时代起</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）</t>
+          <t>乌兹钢（步兵和骑兵攻击无视护甲）；医疗部队（象兵每分钟恢复30生命）</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：医疗部队（象兵每分钟恢复30生命）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>骆驼生命+25%</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>骆驼生命+25%</t>
+          <t>死士（骑兵攻击+5）</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骠骑兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系对远程士兵的攻击力 +1；列克提克遗产（斥候系可造成践踏伤害）</t>
+          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）；奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：斥候骑兵系对远程士兵的攻击力 +1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
+          <t>宝伞（象兵生命+100）</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="51" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>宝伞（象兵生命+100）</t>
+          <t>马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>城堡时代起</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：宝伞（象兵生命+100）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>医疗部队（象兵每分钟恢复30生命）；乌兹钢（步兵和骑兵攻击无视护甲）</t>
+          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1753,17 +1753,17 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：医疗部队（象兵每分钟恢复30生命）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -1773,27 +1773,27 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）；奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
+          <t>封建起骑乘/火枪骑攻速+25%</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>无条件</t>
+          <t>封建时代起</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="51" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>死士（骑兵攻击+5）</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）；斥候系费用-15%</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骠骑兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="51" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -1833,17 +1833,17 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>骑兵杀敌+3黄金；Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>城堡时代起</t>
+          <t>无条件</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
     </row>
@@ -1907,8 +1907,38 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>黑暗时代起</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F38"/>
+  <autoFilter ref="A1:F39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -1920,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2046,22 +2076,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>骑士系视野 +2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>视野提升</t>
         </is>
       </c>
     </row>
@@ -2073,22 +2103,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>骆驼和象兵单位的训练速度 +25%</t>
+          <t>骑兵封建起生命+20%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2100,22 +2130,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
+          <t>骑士精神（马厩工作速度+40%）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -2127,12 +2157,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2142,7 +2172,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2184,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>骑士系对步兵的攻击 +1</t>
+          <t>骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2169,7 +2199,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>训练速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -2181,22 +2211,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+          <t>骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2238,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>明光铠（骑兵单位近战护甲+4）</t>
+          <t>文德尔之遗（骑士系造成践踏伤害）</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2223,7 +2253,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -2235,22 +2265,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>魏</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%</t>
+          <t>骑士系对步兵的攻击 +1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2267,17 +2297,17 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>骑兵对攻城武器的攻击力 +2</t>
+          <t>明光铠（骑兵单位近战护甲+4）</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2319,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王移速+5/10/15%</t>
+          <t>黑光铠/鲜卑掠骑兵城堡/帝王生命+20/30%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2304,7 +2334,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>机动性提升</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -2316,22 +2346,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>魏</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>靶场/马厩木材-75</t>
+          <t>骑兵对攻城武器的攻击力 +2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2373,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2358,7 +2388,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>训练速度提升，成型更快</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2454,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2439,7 +2469,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>持续回血，长期更省维修成本</t>
+          <t>机动性提升</t>
         </is>
       </c>
     </row>
@@ -2451,12 +2481,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
+          <t>大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2466,11 +2496,11 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+          <t>训练速度提升，成型更快</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>B</t>
@@ -2478,22 +2508,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2805,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>西帕希骑兵（骑射手生命+20）</t>
+          <t>掠夺者（马厩训练答刺罕骑兵）</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2790,7 +2820,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>直接强化骑兵</t>
         </is>
       </c>
     </row>
@@ -2807,17 +2837,17 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>掠夺者（马厩训练答刺罕骑兵）</t>
+          <t>马厩工作速度 +20%</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>团队加成</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>直接强化骑兵</t>
+          <t>工作速度提升，成型更快</t>
         </is>
       </c>
     </row>
@@ -2903,9 +2933,9 @@
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2915,7 +2945,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>马厩科技-50%</t>
+          <t>城堡时代可升重装骑士</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2925,7 +2955,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>直接强化骑兵</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2967,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>城堡时代可升重装骑士</t>
+          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2952,7 +2982,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>直接强化骑兵</t>
+          <t>可驻扎，受攻击时更安全</t>
         </is>
       </c>
     </row>
@@ -2991,12 +3021,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
+          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3006,7 +3036,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>可驻扎，受攻击时更安全</t>
+          <t>持续回血，长期更省维修成本</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3048,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>骑士系视野 +2</t>
+          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3033,7 +3063,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>视野提升</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -3045,22 +3075,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建起生命+20%</t>
+          <t>列克提克遗产（斥候系可造成践踏伤害）</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>生命值提升，抗打更久</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -3072,12 +3102,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3087,7 +3117,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -3099,12 +3129,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
+          <t>兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3114,7 +3144,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>持续回血，长期更省维修成本</t>
+          <t>提前解锁，抢一个时代的节奏</t>
         </is>
       </c>
     </row>
@@ -3131,17 +3161,17 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>步兵护甲升级适用于骑兵</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3183,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>兵营/靶场/马厩可用招募训令</t>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3168,7 +3198,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>提前解锁，抢一个时代的节奏</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -3180,12 +3210,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>步兵护甲升级适用于骑兵</t>
+          <t>骑兵杀敌+3黄金</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3195,7 +3225,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
@@ -3207,22 +3237,22 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
+          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>穿透伤害，对高护甲目标有效</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3264,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3249,7 +3279,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
+          <t>附加范围/冲击伤害，团战更占优</t>
         </is>
       </c>
     </row>
@@ -3288,12 +3318,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）</t>
+          <t>医疗部队（象兵每分钟恢复30生命）</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3303,7 +3333,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>生命值提升，抗打更久</t>
         </is>
       </c>
     </row>
@@ -3315,12 +3345,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>乌兹钢（步兵和骑兵攻击无视护甲）</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3330,7 +3360,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>资源产出/节省，加快成型</t>
+          <t>攻击无视护甲，克制重甲目标</t>
         </is>
       </c>
     </row>
@@ -3362,19 +3392,19 @@
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+          <t>死士（骑兵攻击+5）</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3384,7 +3414,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>减少受到的伤害，正面更耐打</t>
+          <t>攻击力提升，正面更硬</t>
         </is>
       </c>
     </row>
@@ -3396,26 +3426,26 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系对远程士兵的攻击力 +1</t>
+          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
+          <t>护甲提升，减伤更耐打</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
           <t>D</t>
@@ -3423,12 +3453,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>列克提克遗产（斥候系可造成践踏伤害）</t>
+          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3438,7 +3468,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>附加范围/冲击伤害，团战更占优</t>
+          <t>护甲提升，减伤更耐打</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3480,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
+          <t>奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3465,7 +3495,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>额外产出资源，经济滚雪球更快</t>
         </is>
       </c>
     </row>
@@ -3504,12 +3534,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>医疗部队（象兵每分钟恢复30生命）</t>
+          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3523,7 +3553,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="28" customHeight="1">
+    <row r="60" ht="36" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
           <t>D</t>
@@ -3531,49 +3561,49 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>乌兹钢（步兵和骑兵攻击无视护甲）</t>
+          <t>从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>团队加成</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>提供额外单位或升级选项，本流派可用的兵种更多</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
           <t>独特科技</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>攻击无视护甲，克制重甲目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>色雷斯人</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>护甲提升，减伤更耐打</t>
+          <t>减少受到的伤害，正面更耐打</t>
         </is>
       </c>
     </row>
@@ -3585,108 +3615,27 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
+          <t>封建起骑乘/火枪骑攻速+25%</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>额外产出资源，经济滚雪球更快</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>马里</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>死士（骑兵攻击+5）</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>攻击力提升，正面更硬</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>骑兵杀敌+3黄金</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>资源产出/节省，加快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>马普切</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>穿透伤害，对高护甲目标有效</t>
+          <t>攻速提升，直接抬高输出</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E65"/>
+  <autoFilter ref="A1:E62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -3698,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3736,83 +3685,83 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>法兰克</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>王家敕令骑兵（骑马弩手黄金-40%）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>瞿折罗</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>刹帝利（军事单位食物-25%）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>格鲁吉亚</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>柏柏尔</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>马厩单位城堡/帝王费用-15/20%</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>库曼</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>靶场/马厩木材-75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>土耳其</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
@@ -3824,49 +3773,49 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>马厩工作速度 +20%</t>
+          <t>阿兹瑙里骑兵（骑兵人口-20%）</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>团队加成</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>工作速度提升，成型更快</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>骑士精神（马厩工作速度+40%）</t>
+          <t>马厩科技-50%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>工作速度提升，成型更快</t>
+          <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
@@ -3878,12 +3827,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>骆驼/掷矛/长矛兵费用-25%</t>
+          <t>血统/斥候食物费用-50%</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -3905,71 +3854,71 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>斥候系费用-15%</t>
+          <t>贵族特权（骑士黄金费用-60%）</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>马普切</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>独特科技</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>拜占庭</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>骆驼/掷矛/长矛兵费用-25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>血统/斥候食物费用-50%</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>主要功能</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>降低费用，让该流派更快成型</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>波兰</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>贵族特权（骑士黄金费用-60%）</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>独特科技</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -3986,17 +3935,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>布图马普（团队城堡独特单位及掷石绳骑兵成本-15%）</t>
+          <t>马厩单位城堡/帝王费用-15/20%</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>独特科技</t>
+          <t>主要功能</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4013,22 +3962,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>马来</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>象兵城堡/帝王费用-25/35%</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>主要功能</t>
+          <t>独特科技</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>降低费用，让该流派更快成型</t>
+          <t>资源产出/节省，加快成型</t>
         </is>
       </c>
     </row>
@@ -4040,27 +3989,135 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>马扎尔</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>斥候系费用-15%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>免费获得整条升级/科技，等于直接省下这笔研究支出</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>马来</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>象兵城堡/帝王费用-25/35%</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>葡萄牙</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>所有单位黄金费用-20%</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>主要功能</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>降低费用，让该流派更快成型</t>
         </is>
       </c>
     </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>印加</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>主要功能</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>降低费用，让该流派更快成型</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4072,7 +4129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4304,12 +4361,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>骑兵和火药文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -4319,19 +4376,19 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>撒克逊人</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和防御文明</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4341,19 +4398,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「磨坊/伐木场/采矿场费用-50%」）</t>
+          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>撒克逊人</t>
+          <t>蜀</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>步兵和防御文明</t>
+          <t>弓兵和攻城文明</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4363,19 +4420,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>步兵和防御文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「磨坊/木料/采矿场建成后食物+35，石料+10」）</t>
+          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「伐木工产木+食物」）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>蜀</t>
+          <t>斯拉夫</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明</t>
+          <t>步兵和攻城文明</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4385,19 +4442,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>弓兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「伐木工产木+食物」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「农民工作速度+15%」）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>斯拉夫</t>
+          <t>图皮</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>步兵和攻城文明</t>
+          <t>弓兵与步兵文明</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4407,19 +4464,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「农民工作速度+15%」）</t>
+          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「开局每种资源+25」）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>图皮</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4429,7 +4486,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>弓兵与步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「开局每种资源+25」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
@@ -4502,12 +4559,12 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步弓手和火药文明</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -4517,19 +4574,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>步弓手和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>斯巴达</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>步弓手和火药文明</t>
+          <t>步兵文明</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -4539,19 +4596,19 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>步弓手和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「初始村民+3，木材-50，食物-200」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>斯巴达</t>
+          <t>雅典</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>步兵文明</t>
+          <t>步兵和海军文明</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -4561,34 +4618,12 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「进入市政/古典免费获一军事执政官」）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>雅典</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>步兵和海军文明</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>无一条直接加强骑兵</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
           <t>步兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「TC可切换政策风格（经济/海军/军事）」）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4693,7 +4728,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4703,12 +4738,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
+          <t>骑士系视野 +2</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 2）；骑兵科技树 13/20。缺：圣骑士、重装骑士、骑士、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 4 条（强 1）；骑兵科技树 13/20。缺：骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -4718,47 +4753,47 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>13/20</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 2）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+          <t>原生条目 4 条（强 2）；骑兵科技树 13/20。缺：圣骑士、重装骑士、骑士、帝王骆驼兵、草原枪兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18/20</t>
+          <t>14/20</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>原生条目 1 条（强 0）；骑兵科技树 18/20。缺：圣骑士、帝王骆驼兵</t>
+          <t>原生条目 2 条（强 2）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -4787,28 +4822,28 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17/20</t>
+          <t>18/20</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75</t>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 0）；骑兵科技树 17/20。缺：重装骆驼兵、帝王骆驼兵、驯马</t>
+          <t>原生条目 1 条（强 0）；骑兵科技树 18/20。缺：圣骑士、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -4843,22 +4878,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>17/20</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 0）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>原生条目 3 条（强 0）；骑兵科技树 17/20。缺：重装骆驼兵、帝王骆驼兵、驯马</t>
         </is>
       </c>
     </row>
@@ -4868,22 +4903,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16/20</t>
+          <t>14/20</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命；阿兹瑙里骑兵（骑兵人口-20%）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>原生条目 3 条（强 1）；骑兵科技树 16/20。缺：圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵</t>
+          <t>原生条目 2 条（强 0）；骑兵科技树 14/20。缺：圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -4993,22 +5028,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>16/20</t>
+          <t>15/20</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系远程护甲+1且升级免费</t>
+          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>原生条目 2 条（强 1）；骑兵科技树 16/20。缺：圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵</t>
+          <t>原生条目 2 条（强 0）；骑兵科技树 15/20。缺：骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵、精锐草原枪兵</t>
         </is>
       </c>
     </row>
@@ -5128,13 +5163,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>瞿折罗</t>
+          <t>法兰克</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -5149,12 +5184,12 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%；骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
+          <t>骑士系视野 +2；骑兵封建起生命+20%；骑士精神（马厩工作速度+40%）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 2 / 弱 1）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5199,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>瓦兰吉人</t>
+          <t>瞿折罗</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5179,22 +5214,22 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
+          <t>边防部队（骆驼/骑象弓兵近战护甲+4）；骆驼和象兵单位的训练速度 +25%；骑兵封建/城堡/帝王额外伤害+20/30/40%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 6 条（强 2 / 弱 2）；骑兵科技树 13/20；缺 圣骑士、重装骑士、骑士、帝王骆驼兵；最直接一条：边防部队（骆驼/骑象弓兵近战护甲+4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>鞑靼</t>
+          <t>瓦兰吉人</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -5209,12 +5244,12 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
+          <t>文德尔之遗（骑士系造成践踏伤害）；骑士系对步兵的攻击 +1</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 2 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：文德尔之遗（骑士系造成践踏伤害）</t>
         </is>
       </c>
     </row>
@@ -5248,13 +5283,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="51" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>库曼</t>
+          <t>鞑靼</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5269,12 +5304,12 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王移速+5/10/15%；靶场/马厩木材-75；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
+          <t>丝护甲（斥候/草原枪兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 18/20；缺 圣骑士、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5349,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>格鲁吉亚</t>
+          <t>库曼</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5329,22 +5364,22 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
+          <t>骑兵封建/城堡/帝王移速+5/10/15%；大草原畜牧（斥候/草原枪兵/骑射手训练速度+100%）</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 17/20；缺 重装骆驼兵、帝王骆驼兵、驯马</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>柏柏尔</t>
+          <t>格鲁吉亚</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -5359,12 +5394,12 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
+          <t>骑兵封建/城堡/帝王每分钟回2/8/14生命</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 圣骑士、骆驼兵、重装骆驼兵、帝王骆驼兵</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5454,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）；曼尼普尔马（骑兵对远程攻+4）</t>
+          <t>曼尼普尔马（骑兵对远程攻+4）；象兵近战护甲+1/远程护甲+1；象轿（象兵近战护甲+1/远程护甲+1）</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -5479,7 +5514,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）；骑兵对掷矛手攻+2</t>
+          <t>骑兵对掷矛手攻+2；象兵额外受伤-25%且抗招降；派（战车/象兵攻速+20%）</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -5488,13 +5523,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="51" customHeight="1">
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>匈奴</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -5509,12 +5544,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>西帕希骑兵（骑射手生命+20）</t>
+          <t>掠夺者（马厩训练答刺罕骑兵）；马厩工作速度 +20%</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5559,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>匈奴</t>
+          <t>条顿</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -5539,12 +5574,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>掠夺者（马厩训练答刺罕骑兵）</t>
+          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5589,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>条顿</t>
+          <t>阿契美尼德</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -5569,12 +5604,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>步兵/骑兵城堡/帝王近战护甲+1/+2</t>
+          <t>萨加里斯斧（骑兵无法格挡伤害+2）；马厩科技研究+50%</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 骠骑兵、轻骑兵、骆驼兵、重装骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5619,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>阿契美尼德</t>
+          <t>勃艮第</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -5599,22 +5634,22 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>马厩科技研究+50%；萨加里斯斧（骑兵无法格挡伤害+2）</t>
+          <t>城堡时代可升重装骑士</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="51" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>勃艮第</t>
+          <t>立陶宛</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -5629,12 +5664,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>马厩科技-50%；城堡时代可升重装骑士</t>
+          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 0 / 弱 2）；骑兵科技树 14/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
         </is>
       </c>
     </row>
@@ -5668,13 +5703,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="51" customHeight="1">
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>立陶宛</t>
+          <t>普鲁人</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -5689,22 +5724,22 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
+          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：每驻守一件圣物骑士系/烈堤司攻+1（最高+4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="51" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>法兰克</t>
+          <t>波兰</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -5719,22 +5754,22 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>骑士系视野 +2；骑兵封建起生命+20%；王家敕令骑兵（骑马弩手黄金-40%）</t>
+          <t>斥候骑兵系对远程士兵的攻击力 +1；列克提克遗产（斥候系可造成践踏伤害）</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 13/20；缺 骠骑兵、骆驼兵、重装骆驼兵、帝王骆驼兵；最直接一条：骑士系视野 +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：斥候骑兵系对远程士兵的攻击力 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="51" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>普鲁人</t>
+          <t>马其顿人</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -5749,22 +5784,22 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>附近无敌人时马厩单位每分钟回25生命（古典起）</t>
+          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）；步兵护甲升级适用于骑兵；兵营/靶场/马厩可用招募训令</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 10/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>马其顿人</t>
+          <t>吴</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -5779,12 +5814,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>萨里沙骑兵（伙伴骑兵获快速冲锋）；兵营/靶场/马厩可用招募训令；步兵护甲升级适用于骑兵</t>
+          <t>剑士/黑光铠骑兵帝王攻+2</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 2）；骑兵科技树 8/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：萨里沙骑兵（伙伴骑兵获快速冲锋）</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5829,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>吴</t>
+          <t>马普切</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -5809,12 +5844,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>剑士/黑光铠骑兵帝王攻+2</t>
+          <t>骑兵杀敌+3黄金；Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 12/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5859,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>维京</t>
+          <t>拜占庭</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -5839,12 +5874,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 10/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：酋长（步兵对骑兵攻+5，对骆驼+4）</t>
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5919,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>拜占庭</t>
+          <t>达罗毗荼</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -5899,22 +5934,22 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>后勤学（甲胄骑兵和瓦兰吉卫队可造成践踏伤害）</t>
+          <t>乌兹钢（步兵和骑兵攻击无视护甲）；医疗部队（象兵每分钟恢复30生命）</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 帝王骆驼兵、草原枪兵、精锐草原枪兵、血统；最直接一条：骆驼/掷矛/长矛兵费用-25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：医疗部队（象兵每分钟恢复30生命）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>马扎尔</t>
+          <t>萨拉森</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -5929,12 +5964,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>骆驼生命+25%</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5979,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>萨拉森</t>
+          <t>马里</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -5959,12 +5994,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>骆驼生命+25%</t>
+          <t>死士（骑兵攻击+5）</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 15/20；缺 圣骑士、重装骑士、帝王骆驼兵、草原枪兵；最直接一条：骆驼生命+25%</t>
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骠骑兵、帝王骆驼兵、草原枪兵</t>
         </is>
       </c>
     </row>
@@ -5974,7 +6009,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>埃塞俄比亚</t>
+          <t>西西里</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -5989,12 +6024,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6039,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>波兰</t>
+          <t>色雷斯人</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -6019,22 +6054,22 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>斥候骑兵系对远程士兵的攻击力 +1；列克提克遗产（斥候系可造成践踏伤害）</t>
+          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）；奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 5 条（强 1 / 弱 3）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：斥候骑兵系对远程士兵的攻击力 +1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>西西里</t>
+          <t>越南</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -6049,22 +6084,22 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
+          <t>宝伞（象兵生命+100）</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 13/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：锁子甲（骑士系近战护甲+1/远程护甲+2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：宝伞（象兵生命+100）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="51" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>越南</t>
+          <t>柏柏尔</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -6079,12 +6114,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>宝伞（象兵生命+100）</t>
+          <t>马格里布骆驼（骆驼每分钟恢复15生命）；从城堡时代开始，靶场提供标枪骑兵</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 12/20；缺 圣骑士、骠骑兵、骆驼兵、重装骆驼兵；最直接一条：宝伞（象兵生命+100）</t>
+          <t>阶段1·本体强化；原生条目 4 条（强 1 / 弱 1）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：马格里布骆驼（骆驼每分钟恢复15生命）</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6129,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>达罗毗荼</t>
+          <t>埃塞俄比亚</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -6109,22 +6144,22 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>医疗部队（象兵每分钟恢复30生命）；乌兹钢（步兵和骑兵攻击无视护甲）</t>
+          <t>龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：医疗部队（象兵每分钟恢复30生命）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="51" customHeight="1">
+          <t>阶段1·本体强化；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：龙脉（弯刀勇士和骆驼骑兵受骑兵伤害-3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>色雷斯人</t>
+          <t>女真</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -6139,22 +6174,22 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）；奥多曼蒂突袭者（步兵/骑兵杀敌获金）</t>
+          <t>封建起骑乘/火枪骑攻速+25%</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 9/20；缺 圣骑士、重装骑士、骑士、骠骑兵；最直接一条：贝锡安金属利用（征兵系/长矛骑兵系/长柄逆刃刀攻击撕裂目标护甲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
+          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 0）；骑兵科技树 14/20；缺 圣骑士、重装骑士、骑士、骆驼兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="51" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>马扎尔</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -6169,22 +6204,22 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>死士（骑兵攻击+5）</t>
+          <t>科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）；斥候系费用-15%</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 14/20；缺 圣骑士、骠骑兵、帝王骆驼兵、草原枪兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
+          <t>阶段2·减费用；原生条目 3 条（强 1 / 弱 1）；骑兵科技树 15/20；缺 骆驼兵、重装骆驼兵、帝王骆驼兵、草原枪兵；最直接一条：科维尼安军队（马扎尔骠骑消耗额外食物而非黄金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="51" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>马普切</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -6199,12 +6234,12 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>骑兵杀敌+3黄金；Malon突袭（掷石绳骑兵/投石手/掷矛手可穿透伤害）</t>
+          <t>斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>阶段1·本体强化；原生条目 3 条（强 0 / 弱 3）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
+          <t>阶段2·减费用；原生条目 2 条（强 1 / 弱 0）；骑兵科技树 16/20；缺 圣骑士、帝王骆驼兵、草原枪兵、精锐草原枪兵；最直接一条：斥候骑兵系远程护甲+1且升级免费</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6309,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>阿兹特克</t>
+          <t>印加</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -6284,17 +6319,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>不建议</t>
+          <t>2000 金</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>无一条直接加强骑兵</t>
+          <t>军事单位黑暗/封建/城堡/帝王食物-15/20/25/30%</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「初始黄金+50」）</t>
+          <t>阶段2·减费用；原生条目 1 条（强 0 / 弱 1）；骑兵科技树 4/20；缺 圣骑士、重装骑士、骑士、骠骑兵</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6339,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>波希米亚</t>
+          <t>阿兹特克</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -6324,7 +6359,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「采矿场科技免费」）</t>
+          <t>步兵和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「初始黄金+50」）</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6369,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>不列颠</t>
+          <t>波希米亚</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -6354,7 +6389,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>步弓手文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「采矿场科技免费」）</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6399,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>丹麦人</t>
+          <t>不列颠</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -6384,7 +6419,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
+          <t>步弓手文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「羊倌工作速度+25%」）</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6429,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>高丽</t>
+          <t>丹麦人</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -6414,7 +6449,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>防御和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「石矿工速度+20%」）</t>
+          <t>步兵和攻城文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「捕鱼船/村民存食+5%」）</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6459,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>哥特</t>
+          <t>高丽</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -6444,7 +6479,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「可立即研究织布机」）</t>
+          <t>防御和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「石矿工速度+20%」）</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6489,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>凯尔特</t>
+          <t>哥特</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -6474,7 +6509,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「伐木工速度+15%」）</t>
+          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「可立即研究织布机」）</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6519,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>玛雅</t>
+          <t>凯尔特</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -6504,7 +6539,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>弓兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
+          <t>步兵和攻城武器文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「伐木工速度+15%」）</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6549,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>穆伊斯卡</t>
+          <t>玛雅</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -6534,7 +6569,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「升时代黄金-50%」）</t>
+          <t>弓兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「开局村民+1，食物-50」）</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6579,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>女真</t>
+          <t>穆伊斯卡</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -6564,7 +6599,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>骑兵和火药文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「猎物/牲畜肉不腐烂」）</t>
+          <t>弓兵与僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「升时代黄金-50%」）</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6759,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>维京</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -6744,7 +6779,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「建筑工速度+30%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「独轮推车/手推车免费」）</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6789,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>亚美尼亚</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -6774,7 +6809,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「骡车费用-25%」）</t>
+          <t>火药和僧侣文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「建筑工速度+30%」）</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6819,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>亚美尼亚</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -6804,7 +6839,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>弓兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「升时代费用-15%」）</t>
+          <t>步兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「骡车费用-25%」）</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6849,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>印加</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -6834,7 +6869,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>步兵文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「房屋/聚落人口+5」）</t>
+          <t>弓兵和海军文明；本表 450 条中无一条直接作用于骑兵。（它最强的一条功能是「升时代费用-15%」）</t>
         </is>
       </c>
     </row>
